--- a/c.xlsx
+++ b/c.xlsx
@@ -3857,12 +3857,12 @@
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374666</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36 kg</t>
         </is>
       </c>
       <c r="L39" s="10" t="inlineStr"/>
@@ -8272,12 +8272,12 @@
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374142</t>
         </is>
       </c>
       <c r="N91" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="O91" s="10" t="inlineStr"/>
@@ -9647,12 +9647,12 @@
       </c>
       <c r="J124" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374310</t>
         </is>
       </c>
       <c r="K124" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="L124" s="10" t="n">
@@ -9715,12 +9715,12 @@
       </c>
       <c r="AB124" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374252</t>
         </is>
       </c>
       <c r="AC124" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="AD124" s="10" t="n">
@@ -9819,12 +9819,12 @@
       </c>
       <c r="Y125" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374140</t>
         </is>
       </c>
       <c r="Z125" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="AA125" s="10" t="n">
@@ -10800,12 +10800,12 @@
       </c>
       <c r="P136" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>125879</t>
         </is>
       </c>
       <c r="Q136" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="R136" s="10" t="inlineStr"/>
@@ -10898,12 +10898,12 @@
       </c>
       <c r="J138" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374179</t>
         </is>
       </c>
       <c r="K138" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>41.0 kg</t>
         </is>
       </c>
       <c r="L138" s="10" t="n">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="M138" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>125880</t>
         </is>
       </c>
       <c r="N138" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>43.0 kg</t>
         </is>
       </c>
       <c r="O138" s="10" t="n">
@@ -11487,12 +11487,12 @@
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374141</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>47.0 kg</t>
         </is>
       </c>
       <c r="F143" s="10" t="n">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="J154" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374249</t>
         </is>
       </c>
       <c r="K154" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="L154" s="10" t="n">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="M154" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374143</t>
         </is>
       </c>
       <c r="N154" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="O154" s="10" t="n">
@@ -12537,12 +12537,12 @@
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>286475</t>
         </is>
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>48.0 kg</t>
         </is>
       </c>
       <c r="I155" s="10" t="n">
@@ -12925,12 +12925,12 @@
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>286478</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>45 kg</t>
         </is>
       </c>
       <c r="F158" s="10" t="n">
@@ -13616,12 +13616,12 @@
       </c>
       <c r="P166" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374136</t>
         </is>
       </c>
       <c r="Q166" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="R166" s="10" t="inlineStr"/>
@@ -13719,12 +13719,12 @@
       </c>
       <c r="V167" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374253</t>
         </is>
       </c>
       <c r="W167" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>45.0 kg</t>
         </is>
       </c>
       <c r="X167" s="10" t="n">
@@ -26886,12 +26886,12 @@
       </c>
       <c r="H25" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374666</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36 kg</t>
         </is>
       </c>
       <c r="J25" s="17" t="inlineStr"/>
@@ -29984,12 +29984,12 @@
       </c>
       <c r="K57" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374142</t>
         </is>
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="M57" s="17" t="inlineStr"/>
@@ -30671,12 +30671,12 @@
       </c>
       <c r="H75" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374310</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="J75" s="17" t="n">
@@ -30739,12 +30739,12 @@
       </c>
       <c r="Z75" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374252</t>
         </is>
       </c>
       <c r="AA75" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="AB75" s="17" t="n">
@@ -30838,12 +30838,12 @@
       </c>
       <c r="W76" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374140</t>
         </is>
       </c>
       <c r="X76" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="Y76" s="17" t="n">
@@ -31524,12 +31524,12 @@
       </c>
       <c r="N82" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>125879</t>
         </is>
       </c>
       <c r="O82" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="P82" s="17" t="inlineStr"/>
@@ -31612,12 +31612,12 @@
       </c>
       <c r="H84" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374179</t>
         </is>
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>41.0 kg</t>
         </is>
       </c>
       <c r="J84" s="17" t="n">
@@ -31625,12 +31625,12 @@
       </c>
       <c r="K84" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>125880</t>
         </is>
       </c>
       <c r="L84" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>43.0 kg</t>
         </is>
       </c>
       <c r="M84" s="17" t="n">
@@ -32179,12 +32179,12 @@
       </c>
       <c r="B89" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374141</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>47.0 kg</t>
         </is>
       </c>
       <c r="D89" s="17" t="n">
@@ -32817,12 +32817,12 @@
       </c>
       <c r="H95" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374249</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="J95" s="17" t="n">
@@ -32830,12 +32830,12 @@
       </c>
       <c r="K95" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374143</t>
         </is>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="M95" s="17" t="n">
@@ -32926,12 +32926,12 @@
       </c>
       <c r="E96" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>286475</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>48.0 kg</t>
         </is>
       </c>
       <c r="G96" s="17" t="n">
@@ -33302,12 +33302,12 @@
       </c>
       <c r="B99" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>286478</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>45 kg</t>
         </is>
       </c>
       <c r="D99" s="17" t="n">
@@ -33710,12 +33710,12 @@
       </c>
       <c r="N102" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374136</t>
         </is>
       </c>
       <c r="O102" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="P102" s="17" t="inlineStr"/>
@@ -33808,12 +33808,12 @@
       </c>
       <c r="T103" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374253</t>
         </is>
       </c>
       <c r="U103" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>45.0 kg</t>
         </is>
       </c>
       <c r="V103" s="17" t="n">
@@ -38306,7 +38306,7 @@
         <v>24</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>2491</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -38426,7 +38426,7 @@
         <v>34</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>1393</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -38516,7 +38516,7 @@
         <v>25</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>2533</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -38546,7 +38546,7 @@
         <v>26</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>2838</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -38576,7 +38576,7 @@
         <v>20</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>3043</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -38606,7 +38606,7 @@
         <v>16</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>3349</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -45198,17 +45198,17 @@
       </c>
       <c r="D178" s="32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374666</t>
         </is>
       </c>
       <c r="E178" s="30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F178" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36 kg</t>
         </is>
       </c>
       <c r="G178" s="30" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="J178" s="30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -53890,17 +53890,17 @@
       </c>
       <c r="D382" s="32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374142</t>
         </is>
       </c>
       <c r="E382" s="30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F382" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="G382" s="30" t="inlineStr">
@@ -53920,7 +53920,7 @@
       </c>
       <c r="J382" s="30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -55051,17 +55051,17 @@
       </c>
       <c r="D409" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374310</t>
         </is>
       </c>
       <c r="E409" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F409" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="G409" s="28" t="inlineStr">
@@ -55081,7 +55081,7 @@
       </c>
       <c r="J409" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -55266,17 +55266,17 @@
       </c>
       <c r="D414" s="32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374252</t>
         </is>
       </c>
       <c r="E414" s="30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F414" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G414" s="30" t="inlineStr">
@@ -55296,7 +55296,7 @@
       </c>
       <c r="J414" s="30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -55567,17 +55567,17 @@
       </c>
       <c r="D421" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374140</t>
         </is>
       </c>
       <c r="E421" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F421" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G421" s="28" t="inlineStr">
@@ -55597,7 +55597,7 @@
       </c>
       <c r="J421" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -57717,17 +57717,17 @@
       </c>
       <c r="D471" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>125879</t>
         </is>
       </c>
       <c r="E471" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F471" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G471" s="28" t="inlineStr">
@@ -57747,7 +57747,7 @@
       </c>
       <c r="J471" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -57846,17 +57846,17 @@
       </c>
       <c r="D474" s="32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374179</t>
         </is>
       </c>
       <c r="E474" s="30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F474" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>41.0 kg</t>
         </is>
       </c>
       <c r="G474" s="30" t="inlineStr">
@@ -57876,7 +57876,7 @@
       </c>
       <c r="J474" s="30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -57889,17 +57889,17 @@
       </c>
       <c r="D475" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>125880</t>
         </is>
       </c>
       <c r="E475" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F475" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>43.0 kg</t>
         </is>
       </c>
       <c r="G475" s="28" t="inlineStr">
@@ -57919,7 +57919,7 @@
       </c>
       <c r="J475" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -59609,17 +59609,17 @@
       </c>
       <c r="D515" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374141</t>
         </is>
       </c>
       <c r="E515" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F515" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>47.0 kg</t>
         </is>
       </c>
       <c r="G515" s="28" t="inlineStr">
@@ -59639,7 +59639,7 @@
       </c>
       <c r="J515" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -61501,17 +61501,17 @@
       </c>
       <c r="D559" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374249</t>
         </is>
       </c>
       <c r="E559" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F559" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G559" s="28" t="inlineStr">
@@ -61531,7 +61531,7 @@
       </c>
       <c r="J559" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -61544,17 +61544,17 @@
       </c>
       <c r="D560" s="32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374143</t>
         </is>
       </c>
       <c r="E560" s="30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F560" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="G560" s="30" t="inlineStr">
@@ -61574,7 +61574,7 @@
       </c>
       <c r="J560" s="30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -61845,17 +61845,17 @@
       </c>
       <c r="D567" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>286475</t>
         </is>
       </c>
       <c r="E567" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F567" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>48.0 kg</t>
         </is>
       </c>
       <c r="G567" s="28" t="inlineStr">
@@ -61875,7 +61875,7 @@
       </c>
       <c r="J567" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -63049,17 +63049,17 @@
       </c>
       <c r="D595" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>286478</t>
         </is>
       </c>
       <c r="E595" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F595" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>45 kg</t>
         </is>
       </c>
       <c r="G595" s="28" t="inlineStr">
@@ -63079,7 +63079,7 @@
       </c>
       <c r="J595" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -64339,17 +64339,17 @@
       </c>
       <c r="D625" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374136</t>
         </is>
       </c>
       <c r="E625" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F625" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G625" s="28" t="inlineStr">
@@ -64369,7 +64369,7 @@
       </c>
       <c r="J625" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -64597,17 +64597,17 @@
       </c>
       <c r="D631" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374253</t>
         </is>
       </c>
       <c r="E631" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F631" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>45.0 kg</t>
         </is>
       </c>
       <c r="G631" s="28" t="inlineStr">
@@ -64627,7 +64627,7 @@
       </c>
       <c r="J631" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
